--- a/Thermo/Solutions/solution_models_H18.xlsx
+++ b/Thermo/Solutions/solution_models_H18.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xinzh\Dropbox\On_Going_Things\MultiScale_Project\PFM_Run\Thermo\Solutions\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xinzh\Dropbox\On_Going_Things\MultiScale_Project\PFM_Repo\Thermo\Solutions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BDE2F62-EEDD-4625-BABA-7CBC1CD8E275}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3AE782D-AFA6-41FD-B62E-CDD346EFCB1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="865" firstSheet="20" activeTab="26" xr2:uid="{5AA2B440-0145-4F56-AB97-83AB8C8EBBCD}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="865" firstSheet="28" activeTab="37" xr2:uid="{5AA2B440-0145-4F56-AB97-83AB8C8EBBCD}"/>
   </bookViews>
   <sheets>
     <sheet name="Melt (Ab-An)" sheetId="50" r:id="rId1"/>
@@ -608,12 +608,6 @@
     <t>Y</t>
   </si>
   <si>
-    <t>msto</t>
-  </si>
-  <si>
-    <t>mstt</t>
-  </si>
-  <si>
     <t>mnst2</t>
   </si>
   <si>
@@ -1080,12 +1074,6 @@
   </si>
   <si>
     <t>mnst2,tc-ds633</t>
-  </si>
-  <si>
-    <t>msto,tc-ds633</t>
-  </si>
-  <si>
-    <t>mstt,tc-ds633</t>
   </si>
   <si>
     <t>mctd,tc-ds633</t>
@@ -1289,6 +1277,18 @@
   <si>
     <t>Al</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>msto,tc-ds633</t>
+  </si>
+  <si>
+    <t>mstt,tc-ds633</t>
+  </si>
+  <si>
+    <t>msto</t>
+  </si>
+  <si>
+    <t>mstt</t>
   </si>
 </sst>
 </file>
@@ -1659,7 +1659,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B1">
         <v>1</v>
@@ -1667,7 +1667,7 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B3" t="s">
         <v>12</v>
@@ -1692,7 +1692,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="B6" s="1">
         <v>1</v>
@@ -1704,7 +1704,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="B7" s="1">
         <v>0</v>
@@ -1716,7 +1716,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B9">
         <v>1</v>
@@ -1727,7 +1727,7 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -1738,7 +1738,7 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B12">
         <v>1</v>
@@ -1749,7 +1749,7 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B13">
         <v>6.7000000000000004E-2</v>
@@ -1760,7 +1760,7 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -1777,7 +1777,7 @@
         <v>94</v>
       </c>
       <c r="C16" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
@@ -1793,7 +1793,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="B18" s="1">
         <v>0</v>
@@ -1815,7 +1815,7 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B1">
         <v>1</v>
@@ -1823,7 +1823,7 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B3" t="s">
         <v>12</v>
@@ -1878,7 +1878,7 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B6" s="1">
         <v>2</v>
@@ -1906,7 +1906,7 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B7" s="1">
         <v>0</v>
@@ -1933,7 +1933,7 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B8" s="1">
         <v>2</v>
@@ -1973,7 +1973,7 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B10">
         <v>2</v>
@@ -2002,7 +2002,7 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -2028,7 +2028,7 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B13">
         <v>1</v>
@@ -2054,7 +2054,7 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B14">
         <v>6.7000000000000004E-2</v>
@@ -2080,7 +2080,7 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -2120,7 +2120,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B1">
         <v>1</v>
@@ -2128,7 +2128,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B3" t="s">
         <v>88</v>
@@ -2140,10 +2140,10 @@
         <v>88</v>
       </c>
       <c r="E3" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="F3" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
@@ -2168,7 +2168,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -2188,7 +2188,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -2208,7 +2208,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -2228,7 +2228,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B10">
         <v>1</v>
@@ -2248,7 +2248,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -2268,7 +2268,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B13">
         <v>1</v>
@@ -2288,7 +2288,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B14">
         <v>6.7000000000000004E-2</v>
@@ -2308,7 +2308,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -2331,7 +2331,7 @@
         <v>5</v>
       </c>
       <c r="B17" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="C17" t="s">
         <v>94</v>
@@ -2342,7 +2342,7 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -2387,7 +2387,7 @@
         <v>6</v>
       </c>
       <c r="B22" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="C22" t="s">
         <v>94</v>
@@ -2398,7 +2398,7 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -2443,7 +2443,7 @@
         <v>7</v>
       </c>
       <c r="B27" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="C27" t="s">
         <v>94</v>
@@ -2454,7 +2454,7 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -2499,7 +2499,7 @@
         <v>8</v>
       </c>
       <c r="B32" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="C32" t="s">
         <v>94</v>
@@ -2563,7 +2563,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B1">
         <v>1</v>
@@ -2571,7 +2571,7 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B3" t="s">
         <v>88</v>
@@ -2599,7 +2599,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -2613,7 +2613,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -2627,7 +2627,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -2641,7 +2641,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B10">
         <v>1</v>
@@ -2655,7 +2655,7 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -2669,7 +2669,7 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B13">
         <v>1</v>
@@ -2683,7 +2683,7 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B14">
         <v>6.7000000000000004E-2</v>
@@ -2697,7 +2697,7 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -2954,7 +2954,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B1">
         <v>1</v>
@@ -2962,7 +2962,7 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B3" t="s">
         <v>88</v>
@@ -2990,7 +2990,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -3004,7 +3004,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -3018,7 +3018,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -3032,7 +3032,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B10">
         <v>1</v>
@@ -3046,7 +3046,7 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -3060,7 +3060,7 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B13">
         <v>1</v>
@@ -3074,7 +3074,7 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B14">
         <v>6.7000000000000004E-2</v>
@@ -3088,7 +3088,7 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -3337,7 +3337,7 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B1">
         <v>1</v>
@@ -3345,7 +3345,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B3" t="s">
         <v>0</v>
@@ -3367,7 +3367,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -3378,7 +3378,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -3389,7 +3389,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B9">
         <v>1</v>
@@ -3400,7 +3400,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -3411,7 +3411,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B12">
         <v>1</v>
@@ -3422,7 +3422,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B13">
         <v>6.7000000000000004E-2</v>
@@ -3433,7 +3433,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -3455,7 +3455,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B1">
         <v>1</v>
@@ -3463,7 +3463,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B3" t="s">
         <v>12</v>
@@ -3497,7 +3497,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B6" s="1">
         <v>1</v>
@@ -3514,7 +3514,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B7" s="1">
         <v>0</v>
@@ -3531,7 +3531,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B8" s="1">
         <v>1</v>
@@ -3548,7 +3548,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B10">
         <v>1</v>
@@ -3565,7 +3565,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -3582,7 +3582,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B13">
         <v>1</v>
@@ -3599,7 +3599,7 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B14">
         <v>0.01</v>
@@ -3616,7 +3616,7 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -3700,7 +3700,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B1">
         <v>1</v>
@@ -3708,7 +3708,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B3" t="s">
         <v>12</v>
@@ -3726,7 +3726,7 @@
         <v>17</v>
       </c>
       <c r="G3" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
@@ -3749,12 +3749,12 @@
         <v>13</v>
       </c>
       <c r="G4" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B6" s="1">
         <v>1</v>
@@ -3777,7 +3777,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B7" s="1">
         <v>0</v>
@@ -3800,7 +3800,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B8" s="1">
         <v>1</v>
@@ -3823,7 +3823,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B9" s="1">
         <v>1</v>
@@ -3846,7 +3846,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B11">
         <v>1</v>
@@ -3869,7 +3869,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -3892,7 +3892,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B14">
         <v>1</v>
@@ -3915,7 +3915,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B15">
         <v>0.03</v>
@@ -3938,7 +3938,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -4057,7 +4057,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B1">
         <v>1</v>
@@ -4065,7 +4065,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B3" t="s">
         <v>12</v>
@@ -4105,7 +4105,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B6" s="1">
         <v>1</v>
@@ -4125,7 +4125,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B7" s="1">
         <v>0</v>
@@ -4145,7 +4145,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B8" s="1">
         <v>1</v>
@@ -4165,7 +4165,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B9" s="1">
         <v>1</v>
@@ -4185,7 +4185,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B11">
         <v>1</v>
@@ -4205,7 +4205,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -4225,7 +4225,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B14">
         <v>1</v>
@@ -4245,7 +4245,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B15">
         <v>0.01</v>
@@ -4265,7 +4265,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -4384,7 +4384,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B1">
         <v>1</v>
@@ -4392,7 +4392,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B3" t="s">
         <v>88</v>
@@ -4438,7 +4438,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -4461,7 +4461,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B7" s="1">
         <v>0.5</v>
@@ -4484,7 +4484,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -4507,7 +4507,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B10">
         <v>1</v>
@@ -4530,7 +4530,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -4553,7 +4553,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B13">
         <v>1</v>
@@ -4576,7 +4576,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B14">
         <v>6.7000000000000004E-2</v>
@@ -4599,7 +4599,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -4698,7 +4698,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B1">
         <v>1</v>
@@ -4706,7 +4706,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B3" t="s">
         <v>0</v>
@@ -4722,7 +4722,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -4730,7 +4730,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -4738,7 +4738,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -4746,7 +4746,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B11">
         <v>1</v>
@@ -4754,7 +4754,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B12">
         <v>6.7000000000000004E-2</v>
@@ -4762,7 +4762,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -4784,7 +4784,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B1">
         <v>1</v>
@@ -4792,7 +4792,7 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B3" t="s">
         <v>12</v>
@@ -4817,7 +4817,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B6" s="1">
         <v>0</v>
@@ -4829,7 +4829,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B7" s="1">
         <v>2</v>
@@ -4841,7 +4841,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B9">
         <v>1</v>
@@ -4852,7 +4852,7 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -4863,7 +4863,7 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B12">
         <v>1</v>
@@ -4874,7 +4874,7 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B13">
         <v>0.01</v>
@@ -4885,7 +4885,7 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -4943,7 +4943,7 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B1">
         <v>3</v>
@@ -4951,7 +4951,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B3" t="s">
         <v>0</v>
@@ -4973,7 +4973,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -4984,7 +4984,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -4995,7 +4995,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B9">
         <v>1</v>
@@ -5006,7 +5006,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -5017,7 +5017,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B12">
         <v>1</v>
@@ -5028,7 +5028,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B13">
         <v>6.7000000000000004E-2</v>
@@ -5039,7 +5039,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -5204,7 +5204,7 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B1">
         <v>1</v>
@@ -5212,7 +5212,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B3" t="s">
         <v>0</v>
@@ -5226,7 +5226,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="C4" t="s">
         <v>3</v>
@@ -5234,7 +5234,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -5245,7 +5245,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -5256,7 +5256,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B9">
         <v>1</v>
@@ -5267,7 +5267,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -5278,7 +5278,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B12">
         <v>1</v>
@@ -5289,7 +5289,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B13">
         <f>1/15</f>
@@ -5302,7 +5302,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -5467,7 +5467,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B1">
         <v>1</v>
@@ -5475,7 +5475,7 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B3" t="s">
         <v>0</v>
@@ -5492,7 +5492,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="C4" t="s">
         <v>4</v>
@@ -5503,7 +5503,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -5517,7 +5517,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -5531,7 +5531,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -5545,7 +5545,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B10">
         <v>1</v>
@@ -5559,7 +5559,7 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -5573,7 +5573,7 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B13">
         <v>1</v>
@@ -5587,7 +5587,7 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B14">
         <f>1/15</f>
@@ -5604,7 +5604,7 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -5629,7 +5629,7 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B1">
         <v>1</v>
@@ -5637,7 +5637,7 @@
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B3" t="s">
         <v>12</v>
@@ -5719,7 +5719,7 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -5760,7 +5760,7 @@
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -5801,7 +5801,7 @@
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -5842,7 +5842,7 @@
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B9">
         <v>1</v>
@@ -5883,7 +5883,7 @@
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -5924,7 +5924,7 @@
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -5965,7 +5965,7 @@
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B12">
         <v>0.5</v>
@@ -6006,7 +6006,7 @@
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -6047,7 +6047,7 @@
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B15">
         <v>1</v>
@@ -6088,7 +6088,7 @@
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -6129,7 +6129,7 @@
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B18">
         <v>1</v>
@@ -6170,7 +6170,7 @@
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B19">
         <v>0.05</v>
@@ -6211,7 +6211,7 @@
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -6901,7 +6901,7 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B1">
         <v>1</v>
@@ -6909,7 +6909,7 @@
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B3" t="s">
         <v>12</v>
@@ -6991,7 +6991,7 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -7032,7 +7032,7 @@
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -7073,7 +7073,7 @@
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -7114,7 +7114,7 @@
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B9">
         <v>1</v>
@@ -7155,7 +7155,7 @@
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -7196,7 +7196,7 @@
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -7237,7 +7237,7 @@
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B12">
         <v>0.5</v>
@@ -7278,7 +7278,7 @@
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -7319,7 +7319,7 @@
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -7360,7 +7360,7 @@
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B16">
         <v>1</v>
@@ -7401,7 +7401,7 @@
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -7442,7 +7442,7 @@
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B19">
         <v>1</v>
@@ -7483,7 +7483,7 @@
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B20">
         <v>0.1</v>
@@ -7524,7 +7524,7 @@
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -8347,7 +8347,7 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B1">
         <v>1</v>
@@ -8355,7 +8355,7 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B3" t="s">
         <v>12</v>
@@ -8407,7 +8407,7 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -8433,7 +8433,7 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -8459,7 +8459,7 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B8">
         <v>3</v>
@@ -8485,7 +8485,7 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -8511,7 +8511,7 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -8537,7 +8537,7 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B12">
         <v>3</v>
@@ -8563,7 +8563,7 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -8589,7 +8589,7 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B15">
         <v>1</v>
@@ -8615,7 +8615,7 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B16">
         <v>0.01</v>
@@ -8641,7 +8641,7 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -9121,7 +9121,7 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B1">
         <v>1</v>
@@ -9129,7 +9129,7 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B3" t="s">
         <v>12</v>
@@ -9187,7 +9187,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -9216,7 +9216,7 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -9245,7 +9245,7 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B8">
         <v>3</v>
@@ -9274,7 +9274,7 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B9">
         <v>3</v>
@@ -9303,7 +9303,7 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -9332,7 +9332,7 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -9361,7 +9361,7 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B13">
         <v>3</v>
@@ -9390,7 +9390,7 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -9419,7 +9419,7 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B16">
         <v>1</v>
@@ -9448,7 +9448,7 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B17">
         <v>0.02</v>
@@ -9477,7 +9477,7 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -10095,7 +10095,7 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B1">
         <v>1</v>
@@ -10103,7 +10103,7 @@
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B3" t="s">
         <v>12</v>
@@ -10191,7 +10191,7 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B6" s="1">
         <v>1</v>
@@ -10235,7 +10235,7 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B7" s="1">
         <v>0</v>
@@ -10279,7 +10279,7 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B8" s="1">
         <v>0</v>
@@ -10323,7 +10323,7 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B9" s="1">
         <v>0</v>
@@ -10367,7 +10367,7 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B10" s="1">
         <v>0.5</v>
@@ -10411,7 +10411,7 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B11" s="1">
         <v>0</v>
@@ -10455,7 +10455,7 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B12" s="1">
         <v>1</v>
@@ -10499,7 +10499,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B13" s="1">
         <v>1</v>
@@ -10543,7 +10543,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B14" s="1">
         <v>0</v>
@@ -10602,7 +10602,7 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B16">
         <v>1</v>
@@ -10646,7 +10646,7 @@
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -10690,7 +10690,7 @@
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B19">
         <v>1</v>
@@ -10734,7 +10734,7 @@
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B20">
         <v>0.04</v>
@@ -10778,7 +10778,7 @@
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -12243,7 +12243,7 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B1">
         <v>1</v>
@@ -12251,7 +12251,7 @@
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B3" t="s">
         <v>12</v>
@@ -12339,7 +12339,7 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B6" s="1">
         <v>1</v>
@@ -12383,7 +12383,7 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B7" s="1">
         <v>0</v>
@@ -12427,7 +12427,7 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B8" s="1">
         <v>0</v>
@@ -12471,7 +12471,7 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B9" s="1">
         <v>0</v>
@@ -12515,7 +12515,7 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B10" s="1">
         <v>0</v>
@@ -12559,7 +12559,7 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B11" s="1">
         <v>0.5</v>
@@ -12603,7 +12603,7 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B12" s="1">
         <v>0</v>
@@ -12647,7 +12647,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B13" s="1">
         <v>1</v>
@@ -12691,7 +12691,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B14" s="1">
         <v>1</v>
@@ -12735,7 +12735,7 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B15" s="1">
         <v>0</v>
@@ -12794,7 +12794,7 @@
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B17">
         <v>1</v>
@@ -12838,7 +12838,7 @@
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -12882,7 +12882,7 @@
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B20">
         <v>1</v>
@@ -12926,7 +12926,7 @@
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B21">
         <v>0.1</v>
@@ -12970,7 +12970,7 @@
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -14640,7 +14640,7 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B1">
         <v>1</v>
@@ -14648,7 +14648,7 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B3" t="s">
         <v>51</v>
@@ -14718,7 +14718,7 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -14753,7 +14753,7 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B7" s="4">
         <v>0</v>
@@ -14788,7 +14788,7 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -14823,7 +14823,7 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -14858,7 +14858,7 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -14893,7 +14893,7 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -14928,7 +14928,7 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B12">
         <v>1</v>
@@ -14963,7 +14963,7 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B13">
         <v>1</v>
@@ -14998,7 +14998,7 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B15">
         <v>1</v>
@@ -15033,7 +15033,7 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -15068,7 +15068,7 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B18">
         <v>1</v>
@@ -15103,7 +15103,7 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B19">
         <f>1/6</f>
@@ -15148,7 +15148,7 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -15458,7 +15458,7 @@
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B1">
         <v>4</v>
@@ -15466,7 +15466,7 @@
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B3" t="s">
         <v>51</v>
@@ -15584,7 +15584,7 @@
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -15643,7 +15643,7 @@
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -15702,7 +15702,7 @@
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -15761,7 +15761,7 @@
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -15820,7 +15820,7 @@
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -15879,7 +15879,7 @@
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -15938,7 +15938,7 @@
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -15997,7 +15997,7 @@
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -16056,7 +16056,7 @@
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -16115,7 +16115,7 @@
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -16174,7 +16174,7 @@
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -16233,7 +16233,7 @@
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -16292,7 +16292,7 @@
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B19">
         <v>1</v>
@@ -16351,7 +16351,7 @@
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -16410,7 +16410,7 @@
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B22">
         <v>1</v>
@@ -16469,7 +16469,7 @@
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B23">
         <v>0.08</v>
@@ -16528,7 +16528,7 @@
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -18361,7 +18361,7 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B1">
         <v>1</v>
@@ -18369,7 +18369,7 @@
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B3" t="s">
         <v>51</v>
@@ -18451,7 +18451,7 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -18492,7 +18492,7 @@
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -18533,7 +18533,7 @@
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -18574,7 +18574,7 @@
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -18615,7 +18615,7 @@
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -18656,7 +18656,7 @@
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -18697,7 +18697,7 @@
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -18738,7 +18738,7 @@
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -18779,7 +18779,7 @@
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -18820,7 +18820,7 @@
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -18861,7 +18861,7 @@
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -18902,7 +18902,7 @@
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B18">
         <v>1</v>
@@ -18943,7 +18943,7 @@
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -18984,7 +18984,7 @@
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B21">
         <v>1</v>
@@ -19025,7 +19025,7 @@
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B22">
         <f>1/3</f>
@@ -19078,7 +19078,7 @@
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B23">
         <v>1</v>
@@ -20501,7 +20501,7 @@
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B1">
         <v>1</v>
@@ -20509,7 +20509,7 @@
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B3" t="s">
         <v>51</v>
@@ -20589,7 +20589,7 @@
         <v>28</v>
       </c>
       <c r="L4" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="M4" t="s">
         <v>4</v>
@@ -20603,7 +20603,7 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -20650,7 +20650,7 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -20697,7 +20697,7 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -20744,7 +20744,7 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -20791,7 +20791,7 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -20838,7 +20838,7 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -20885,7 +20885,7 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -20932,7 +20932,7 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -20979,7 +20979,7 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -21026,7 +21026,7 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -21073,7 +21073,7 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -21120,7 +21120,7 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -21167,7 +21167,7 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -21214,7 +21214,7 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B20">
         <v>1</v>
@@ -21261,7 +21261,7 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -21308,7 +21308,7 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B23">
         <v>1</v>
@@ -21355,7 +21355,7 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B24">
         <f>1/3</f>
@@ -21416,7 +21416,7 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -21496,7 +21496,7 @@
         <v>120</v>
       </c>
       <c r="L27" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="M27" t="s">
         <v>4</v>
@@ -21947,7 +21947,7 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -22112,7 +22112,7 @@
         <v>120</v>
       </c>
       <c r="L42" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="M42" t="s">
         <v>4</v>
@@ -22563,7 +22563,7 @@
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -22728,7 +22728,7 @@
         <v>120</v>
       </c>
       <c r="L57" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="M57" t="s">
         <v>4</v>
@@ -23179,7 +23179,7 @@
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="B68">
         <v>0</v>
@@ -23322,7 +23322,7 @@
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B1">
         <v>1</v>
@@ -23330,7 +23330,7 @@
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B3" t="s">
         <v>88</v>
@@ -23448,7 +23448,7 @@
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -23507,7 +23507,7 @@
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -23566,7 +23566,7 @@
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -23625,7 +23625,7 @@
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B9">
         <v>1</v>
@@ -23684,7 +23684,7 @@
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B10">
         <v>1</v>
@@ -23743,7 +23743,7 @@
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B11">
         <v>1</v>
@@ -23802,7 +23802,7 @@
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B12">
         <v>1</v>
@@ -23861,7 +23861,7 @@
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B13">
         <v>1</v>
@@ -23920,7 +23920,7 @@
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B14">
         <v>1</v>
@@ -23979,7 +23979,7 @@
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -24038,7 +24038,7 @@
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B16">
         <v>1</v>
@@ -24097,7 +24097,7 @@
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B18">
         <v>1</v>
@@ -24156,7 +24156,7 @@
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -24215,7 +24215,7 @@
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B21">
         <v>1</v>
@@ -24274,7 +24274,7 @@
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B22">
         <f>1/3</f>
@@ -24351,7 +24351,7 @@
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -25941,7 +25941,7 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B1">
         <v>1</v>
@@ -25949,7 +25949,7 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B3" t="s">
         <v>87</v>
@@ -26025,7 +26025,7 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -26063,7 +26063,7 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -26101,7 +26101,7 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -26139,7 +26139,7 @@
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -26177,7 +26177,7 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -26215,7 +26215,7 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -26253,7 +26253,7 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B13">
         <v>1</v>
@@ -26291,7 +26291,7 @@
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -26329,7 +26329,7 @@
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B16">
         <v>1</v>
@@ -26367,7 +26367,7 @@
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B17">
         <f>1/6</f>
@@ -26416,7 +26416,7 @@
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -26626,7 +26626,7 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B1">
         <v>1</v>
@@ -26634,7 +26634,7 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B3" t="s">
         <v>88</v>
@@ -26704,7 +26704,7 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -26739,7 +26739,7 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -26774,7 +26774,7 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -26809,7 +26809,7 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -26844,7 +26844,7 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -26879,7 +26879,7 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B11">
         <v>1</v>
@@ -26914,7 +26914,7 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B13">
         <v>1</v>
@@ -26949,7 +26949,7 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -26984,7 +26984,7 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B16">
         <v>1</v>
@@ -27019,7 +27019,7 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B17">
         <v>6.7000000000000004E-2</v>
@@ -27054,7 +27054,7 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -27677,7 +27677,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B1">
         <v>1</v>
@@ -27685,7 +27685,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B3" t="s">
         <v>12</v>
@@ -27719,7 +27719,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -27736,7 +27736,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -27753,7 +27753,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -27770,7 +27770,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B10">
         <v>1</v>
@@ -27787,7 +27787,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -27804,7 +27804,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B13">
         <v>1</v>
@@ -27822,7 +27822,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B14">
         <v>6.7000000000000004E-2</v>
@@ -27840,7 +27840,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -27951,7 +27951,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B1">
         <v>1</v>
@@ -27959,7 +27959,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B3" t="s">
         <v>156</v>
@@ -27993,7 +27993,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -28010,7 +28010,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B7">
         <v>2</v>
@@ -28027,7 +28027,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -28044,7 +28044,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B10">
         <v>2</v>
@@ -28061,7 +28061,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -28078,7 +28078,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B13">
         <v>1</v>
@@ -28095,7 +28095,7 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B14">
         <v>6.7000000000000004E-2</v>
@@ -28112,7 +28112,7 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -28370,7 +28370,7 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B1">
         <v>1</v>
@@ -28378,7 +28378,7 @@
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B3" t="s">
         <v>12</v>
@@ -28466,7 +28466,7 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -28510,7 +28510,7 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -28554,7 +28554,7 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -28598,7 +28598,7 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -28642,7 +28642,7 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B10">
         <v>1</v>
@@ -28686,7 +28686,7 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -28730,7 +28730,7 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B12">
         <v>1</v>
@@ -28774,7 +28774,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -28818,7 +28818,7 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B15">
         <v>1</v>
@@ -28862,7 +28862,7 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -28906,7 +28906,7 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B18">
         <v>1</v>
@@ -28950,7 +28950,7 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B19">
         <f>1/6</f>
@@ -29007,7 +29007,7 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -29323,7 +29323,7 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B1">
         <v>1</v>
@@ -29331,7 +29331,7 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B3" t="s">
         <v>156</v>
@@ -29383,7 +29383,7 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B6">
         <v>4</v>
@@ -29409,7 +29409,7 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -29435,7 +29435,7 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -29461,7 +29461,7 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>330</v>
+        <v>395</v>
       </c>
       <c r="B9">
         <v>4</v>
@@ -29487,7 +29487,7 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>331</v>
+        <v>396</v>
       </c>
       <c r="B10">
         <v>4</v>
@@ -29515,7 +29515,7 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B12">
         <v>4</v>
@@ -29541,7 +29541,7 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -29567,7 +29567,7 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B15">
         <v>1</v>
@@ -29593,7 +29593,7 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B16">
         <v>6.7000000000000004E-2</v>
@@ -29619,7 +29619,7 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -29648,24 +29648,24 @@
         <v>5</v>
       </c>
       <c r="B19" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C19" t="s">
         <v>170</v>
       </c>
       <c r="D19" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E19" t="s">
-        <v>172</v>
+        <v>397</v>
       </c>
       <c r="F19" t="s">
-        <v>173</v>
+        <v>398</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -29705,7 +29705,7 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B22" s="2">
         <v>12000</v>
@@ -29725,7 +29725,7 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>172</v>
+        <v>397</v>
       </c>
       <c r="B23" s="2">
         <v>2000</v>
@@ -29745,7 +29745,7 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>173</v>
+        <v>398</v>
       </c>
       <c r="B24" s="2">
         <v>20000</v>
@@ -29776,7 +29776,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B1">
         <v>1</v>
@@ -29784,22 +29784,22 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="F3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
@@ -29824,7 +29824,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="B6">
         <f>1/2</f>
@@ -29845,7 +29845,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="B7">
         <f>1/2</f>
@@ -29866,7 +29866,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="B8">
         <f>1/2</f>
@@ -29887,7 +29887,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -29908,7 +29908,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B11">
         <f>1/2</f>
@@ -29930,7 +29930,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -29950,7 +29950,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B14">
         <v>1</v>
@@ -29970,7 +29970,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B15">
         <v>6.7000000000000004E-2</v>
@@ -29990,7 +29990,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -30013,21 +30013,21 @@
         <v>5</v>
       </c>
       <c r="B18" t="s">
+        <v>174</v>
+      </c>
+      <c r="C18" t="s">
+        <v>175</v>
+      </c>
+      <c r="D18" t="s">
+        <v>179</v>
+      </c>
+      <c r="E18" t="s">
         <v>176</v>
-      </c>
-      <c r="C18" t="s">
-        <v>177</v>
-      </c>
-      <c r="D18" t="s">
-        <v>181</v>
-      </c>
-      <c r="E18" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -30044,7 +30044,7 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B20" s="2">
         <v>4000</v>
@@ -30061,7 +30061,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B21" s="2">
         <v>3000</v>
@@ -30078,7 +30078,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B22" s="2">
         <v>1000</v>
@@ -30109,7 +30109,7 @@
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B1">
         <v>4</v>
@@ -30117,7 +30117,7 @@
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B3" t="s">
         <v>51</v>
@@ -30229,7 +30229,7 @@
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -30285,7 +30285,7 @@
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -30341,7 +30341,7 @@
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -30397,7 +30397,7 @@
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -30453,7 +30453,7 @@
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -30509,7 +30509,7 @@
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -30565,7 +30565,7 @@
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -30621,7 +30621,7 @@
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -30677,7 +30677,7 @@
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -30733,7 +30733,7 @@
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -30789,7 +30789,7 @@
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -30845,7 +30845,7 @@
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B18">
         <v>1</v>
@@ -30901,7 +30901,7 @@
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -30957,7 +30957,7 @@
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B21">
         <v>1</v>
@@ -31013,7 +31013,7 @@
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B22">
         <v>0.1</v>
@@ -31069,7 +31069,7 @@
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -32657,7 +32657,7 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B1">
         <v>1</v>
@@ -32665,7 +32665,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B3" t="s">
         <v>0</v>
@@ -32687,7 +32687,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -32698,7 +32698,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -32709,7 +32709,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B9">
         <v>1</v>
@@ -32720,7 +32720,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -32731,7 +32731,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B12">
         <v>1</v>
@@ -32742,7 +32742,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B13">
         <v>6.7000000000000004E-2</v>
@@ -32753,7 +32753,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -32767,15 +32767,15 @@
         <v>5</v>
       </c>
       <c r="B16" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C16" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -32786,7 +32786,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B18" s="2">
         <v>4000</v>
@@ -32808,7 +32808,7 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B1">
         <v>1</v>
@@ -32816,7 +32816,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B3" t="s">
         <v>0</v>
@@ -32838,7 +32838,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -32849,7 +32849,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -32860,7 +32860,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B9">
         <v>1</v>
@@ -32871,7 +32871,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -32882,7 +32882,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B12">
         <v>1</v>
@@ -32893,7 +32893,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B13">
         <v>6.7000000000000004E-2</v>
@@ -32904,7 +32904,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -32918,15 +32918,15 @@
         <v>5</v>
       </c>
       <c r="B16" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C16" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -32937,7 +32937,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B18" s="2">
         <v>3000</v>
@@ -32959,7 +32959,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B1">
         <v>1</v>
@@ -32967,7 +32967,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B3" t="s">
         <v>88</v>
@@ -33007,7 +33007,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -33027,7 +33027,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -33047,7 +33047,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -33067,7 +33067,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B10">
         <v>1</v>
@@ -33087,7 +33087,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -33107,7 +33107,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B13">
         <v>1</v>
@@ -33127,7 +33127,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B14">
         <v>6.7000000000000004E-2</v>
@@ -33147,7 +33147,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -33170,18 +33170,18 @@
         <v>5</v>
       </c>
       <c r="B17" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C17" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D17" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -33195,7 +33195,7 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B19" s="2">
         <v>8000</v>
@@ -33209,7 +33209,7 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B20" s="2">
         <v>6000</v>
@@ -33234,7 +33234,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B1">
         <v>1</v>
@@ -33242,7 +33242,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B3" t="s">
         <v>88</v>
@@ -33282,7 +33282,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -33302,7 +33302,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -33322,7 +33322,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -33342,7 +33342,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B10">
         <v>1</v>
@@ -33362,7 +33362,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -33382,7 +33382,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B13">
         <v>1</v>
@@ -33402,7 +33402,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B14">
         <v>6.7000000000000004E-2</v>
@@ -33422,7 +33422,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -33445,18 +33445,18 @@
         <v>5</v>
       </c>
       <c r="B17" t="s">
+        <v>183</v>
+      </c>
+      <c r="C17" t="s">
+        <v>184</v>
+      </c>
+      <c r="D17" t="s">
         <v>185</v>
-      </c>
-      <c r="C17" t="s">
-        <v>186</v>
-      </c>
-      <c r="D17" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -33470,7 +33470,7 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B19" s="2">
         <v>8000</v>
@@ -33484,7 +33484,7 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B20" s="2">
         <v>6000</v>
@@ -33509,7 +33509,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B1">
         <v>1</v>
@@ -33517,7 +33517,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B3" t="s">
         <v>88</v>
@@ -33557,7 +33557,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -33577,7 +33577,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -33597,7 +33597,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -33617,7 +33617,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B10">
         <v>1</v>
@@ -33637,7 +33637,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -33657,7 +33657,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B13">
         <v>1</v>
@@ -33677,7 +33677,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B14">
         <v>6.7000000000000004E-2</v>
@@ -33697,7 +33697,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -33720,18 +33720,18 @@
         <v>5</v>
       </c>
       <c r="B17" t="s">
+        <v>183</v>
+      </c>
+      <c r="C17" t="s">
+        <v>184</v>
+      </c>
+      <c r="D17" t="s">
         <v>185</v>
-      </c>
-      <c r="C17" t="s">
-        <v>186</v>
-      </c>
-      <c r="D17" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -33745,7 +33745,7 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B19" s="2">
         <v>8000</v>
@@ -33759,7 +33759,7 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B20" s="2">
         <v>6000</v>
@@ -33785,7 +33785,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B1">
         <v>1</v>
@@ -33793,7 +33793,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B3" t="s">
         <v>88</v>
@@ -33833,7 +33833,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -33853,7 +33853,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -33873,7 +33873,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -33893,7 +33893,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B10">
         <v>1</v>
@@ -33913,7 +33913,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -33933,7 +33933,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B13">
         <v>1</v>
@@ -33953,7 +33953,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B14">
         <v>6.7000000000000004E-2</v>
@@ -33973,7 +33973,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -33996,18 +33996,18 @@
         <v>5</v>
       </c>
       <c r="B17" t="s">
+        <v>186</v>
+      </c>
+      <c r="C17" t="s">
+        <v>187</v>
+      </c>
+      <c r="D17" t="s">
         <v>188</v>
-      </c>
-      <c r="C17" t="s">
-        <v>189</v>
-      </c>
-      <c r="D17" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -34021,7 +34021,7 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B19" s="2">
         <v>4000</v>
@@ -34035,7 +34035,7 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B20" s="2">
         <v>20000</v>
@@ -34060,7 +34060,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B1">
         <v>1</v>
@@ -34068,7 +34068,7 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B3" t="s">
         <v>88</v>
@@ -34090,7 +34090,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="B6">
         <v>2</v>
@@ -34101,7 +34101,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -34112,7 +34112,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B9">
         <v>2</v>
@@ -34127,7 +34127,7 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -34139,7 +34139,7 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B12">
         <v>1</v>
@@ -34150,7 +34150,7 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B13">
         <v>6.7000000000000004E-2</v>
@@ -34161,7 +34161,7 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -34175,15 +34175,15 @@
         <v>5</v>
       </c>
       <c r="B16" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C16" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -34194,7 +34194,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B18" s="2">
         <v>4000</v>
@@ -34216,7 +34216,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B1">
         <v>1</v>
@@ -34224,7 +34224,7 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B3" t="s">
         <v>88</v>
@@ -34246,7 +34246,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="B6">
         <v>2</v>
@@ -34257,7 +34257,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -34268,7 +34268,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B9">
         <v>2</v>
@@ -34279,7 +34279,7 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -34291,7 +34291,7 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B12">
         <v>1</v>
@@ -34303,7 +34303,7 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B13">
         <v>6.7000000000000004E-2</v>
@@ -34314,7 +34314,7 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -34328,15 +34328,15 @@
         <v>5</v>
       </c>
       <c r="B16" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C16" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -34347,7 +34347,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B18" s="2">
         <v>13000</v>
@@ -34369,7 +34369,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B1">
         <v>1</v>
@@ -34377,7 +34377,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B3" t="s">
         <v>88</v>
@@ -34423,7 +34423,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B6">
         <v>3</v>
@@ -34446,7 +34446,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -34469,7 +34469,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="B8">
         <v>3</v>
@@ -34492,7 +34492,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="B9">
         <v>3</v>
@@ -34515,7 +34515,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B11">
         <v>3</v>
@@ -34538,7 +34538,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -34561,7 +34561,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B14">
         <v>1</v>
@@ -34584,7 +34584,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B15">
         <v>6.7000000000000004E-2</v>
@@ -34607,7 +34607,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -34639,10 +34639,10 @@
         <v>70</v>
       </c>
       <c r="D18" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E18" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
@@ -34681,7 +34681,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B21" s="2">
         <v>15000</v>
@@ -34698,7 +34698,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B22" s="2">
         <v>15000</v>
@@ -34727,7 +34727,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B1">
         <v>1</v>
@@ -34735,7 +34735,7 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B3" t="s">
         <v>88</v>
@@ -34757,7 +34757,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -34768,7 +34768,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -34782,7 +34782,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B9">
         <v>1</v>
@@ -34794,7 +34794,7 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -34805,7 +34805,7 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B12">
         <v>1</v>
@@ -34816,7 +34816,7 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B13">
         <v>6.7000000000000004E-2</v>
@@ -34827,7 +34827,7 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -34841,15 +34841,15 @@
         <v>5</v>
       </c>
       <c r="B16" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C16" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -34860,7 +34860,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B18" s="2">
         <v>18000</v>
@@ -34885,7 +34885,7 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B1">
         <v>5</v>
@@ -34893,7 +34893,7 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B3" t="s">
         <v>88</v>
@@ -34907,7 +34907,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="C4" t="s">
         <v>3</v>
@@ -34915,7 +34915,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -34926,7 +34926,7 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -34940,7 +34940,7 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B9">
         <v>1</v>
@@ -34959,7 +34959,7 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -34970,7 +34970,7 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B12">
         <v>0.1</v>
@@ -34981,7 +34981,7 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B13">
         <v>1E-3</v>
@@ -34993,7 +34993,7 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B14">
         <v>1</v>
@@ -35023,7 +35023,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B1">
         <v>1</v>
@@ -35031,7 +35031,7 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B3" t="s">
         <v>88</v>
@@ -35047,7 +35047,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -35055,7 +35055,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -35063,7 +35063,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -35071,7 +35071,7 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B11">
         <v>1</v>
@@ -35079,7 +35079,7 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B12">
         <v>6.7000000000000004E-2</v>
@@ -35087,7 +35087,7 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -35124,7 +35124,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B1">
         <v>1</v>
@@ -35132,7 +35132,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B3" t="s">
         <v>88</v>
@@ -35148,7 +35148,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -35156,7 +35156,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -35164,7 +35164,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -35172,7 +35172,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B11">
         <v>1</v>
@@ -35180,7 +35180,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B12">
         <v>6.7000000000000004E-2</v>
@@ -35188,7 +35188,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -35207,7 +35207,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B1">
         <v>1</v>
@@ -35215,7 +35215,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B3" t="s">
         <v>88</v>
@@ -35231,7 +35231,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -35239,7 +35239,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -35247,7 +35247,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -35255,7 +35255,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B11">
         <v>1</v>
@@ -35263,7 +35263,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B12">
         <v>6.7000000000000004E-2</v>
@@ -35271,7 +35271,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -35290,7 +35290,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B1">
         <v>1</v>
@@ -35298,7 +35298,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B3" t="s">
         <v>88</v>
@@ -35314,7 +35314,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -35322,7 +35322,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -35330,7 +35330,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -35338,7 +35338,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B11">
         <v>1</v>
@@ -35346,7 +35346,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B12">
         <v>6.7000000000000004E-2</v>
@@ -35354,7 +35354,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -35373,7 +35373,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B1">
         <v>1</v>
@@ -35381,7 +35381,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B3" t="s">
         <v>88</v>
@@ -35397,7 +35397,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -35405,7 +35405,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -35413,7 +35413,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -35421,7 +35421,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B11">
         <v>1</v>
@@ -35429,7 +35429,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B12">
         <v>6.7000000000000004E-2</v>
@@ -35437,7 +35437,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -35456,7 +35456,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B1">
         <v>1</v>
@@ -35464,7 +35464,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B3" t="s">
         <v>88</v>
@@ -35480,7 +35480,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -35488,7 +35488,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -35496,7 +35496,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -35504,7 +35504,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B11">
         <v>1</v>
@@ -35512,7 +35512,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B12">
         <v>6.7000000000000004E-2</v>
@@ -35520,7 +35520,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -35539,7 +35539,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B1">
         <v>1</v>
@@ -35547,7 +35547,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B3" t="s">
         <v>88</v>
@@ -35563,7 +35563,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -35571,7 +35571,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -35579,7 +35579,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -35587,7 +35587,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B11">
         <v>1</v>
@@ -35595,7 +35595,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B12">
         <v>6.7000000000000004E-2</v>
@@ -35603,7 +35603,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -35622,7 +35622,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B1">
         <v>1</v>
@@ -35630,7 +35630,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B3" t="s">
         <v>88</v>
@@ -35646,7 +35646,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -35654,7 +35654,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -35662,7 +35662,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -35670,7 +35670,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B11">
         <v>1</v>
@@ -35678,7 +35678,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B12">
         <v>6.7000000000000004E-2</v>
@@ -35686,7 +35686,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -35708,7 +35708,7 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B1">
         <v>8</v>
@@ -35716,7 +35716,7 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B3" t="s">
         <v>88</v>
@@ -35742,27 +35742,27 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
+        <v>383</v>
+      </c>
+      <c r="C4" t="s">
+        <v>385</v>
+      </c>
+      <c r="D4" t="s">
+        <v>386</v>
+      </c>
+      <c r="E4" t="s">
+        <v>384</v>
+      </c>
+      <c r="F4" t="s">
         <v>387</v>
       </c>
-      <c r="C4" t="s">
-        <v>389</v>
-      </c>
-      <c r="D4" t="s">
-        <v>390</v>
-      </c>
-      <c r="E4" t="s">
-        <v>388</v>
-      </c>
-      <c r="F4" t="s">
-        <v>391</v>
-      </c>
       <c r="G4" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -35785,7 +35785,7 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -35808,7 +35808,7 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -35831,7 +35831,7 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -35854,7 +35854,7 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -35877,7 +35877,7 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -35903,7 +35903,7 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B13">
         <v>1</v>
@@ -35934,7 +35934,7 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B15" s="2">
         <v>9.9999999999999995E-7</v>
@@ -35957,7 +35957,7 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B16">
         <v>1</v>
@@ -35980,7 +35980,7 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B17">
         <f>(B16-B15)/6</f>
@@ -36009,7 +36009,7 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B18">
         <v>1</v>
@@ -36054,7 +36054,7 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B1">
         <v>5</v>
@@ -36062,7 +36062,7 @@
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B3" t="s">
         <v>88</v>
@@ -36091,22 +36091,22 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="C4" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="D4" t="s">
+        <v>362</v>
+      </c>
+      <c r="E4" t="s">
+        <v>369</v>
+      </c>
+      <c r="F4" t="s">
         <v>366</v>
       </c>
-      <c r="E4" t="s">
-        <v>373</v>
-      </c>
-      <c r="F4" t="s">
-        <v>370</v>
-      </c>
       <c r="G4" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="H4" t="s">
         <v>3</v>
@@ -36114,7 +36114,7 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -36140,7 +36140,7 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -36166,7 +36166,7 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -36192,7 +36192,7 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -36218,7 +36218,7 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -36244,7 +36244,7 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -36270,7 +36270,7 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -36299,7 +36299,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B14">
         <v>1</v>
@@ -36333,7 +36333,7 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -36359,7 +36359,7 @@
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B17">
         <v>1</v>
@@ -36385,7 +36385,7 @@
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B18">
         <f t="shared" ref="B18:H18" si="0">1/15</f>
@@ -36418,7 +36418,7 @@
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -36466,7 +36466,7 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B1">
         <v>5</v>
@@ -36474,7 +36474,7 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B3" t="s">
         <v>88</v>
@@ -36494,13 +36494,13 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="C4" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="D4" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="E4" t="s">
         <v>3</v>
@@ -36508,7 +36508,7 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -36525,7 +36525,7 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -36542,7 +36542,7 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -36559,7 +36559,7 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -36579,7 +36579,7 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B11">
         <v>1</v>
@@ -36604,7 +36604,7 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -36621,7 +36621,7 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B14">
         <v>1</v>
@@ -36638,7 +36638,7 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B15">
         <f>1/15</f>
@@ -36659,7 +36659,7 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -36698,7 +36698,7 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B1">
         <v>1</v>
@@ -36706,7 +36706,7 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B3" t="s">
         <v>0</v>
@@ -36758,7 +36758,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B6" s="1">
         <v>44</v>
@@ -36785,7 +36785,7 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B7" s="1">
         <v>0</v>
@@ -36812,7 +36812,7 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B8" s="1">
         <v>44</v>
@@ -36849,7 +36849,7 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B10">
         <v>44</v>
@@ -36878,7 +36878,7 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -36904,7 +36904,7 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B13">
         <v>1</v>
@@ -36930,7 +36930,7 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B14">
         <v>6.7000000000000004E-2</v>
@@ -36956,7 +36956,7 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B15">
         <v>0</v>
